--- a/data/trans_camb/P2C_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,65; 28,02</t>
+          <t>9,83; 27,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 10,4</t>
+          <t>-7,29; 10,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-44,28; -31,45</t>
+          <t>-43,64; -31,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,56; 35,15</t>
+          <t>15,86; 34,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,78; 28,05</t>
+          <t>9,66; 27,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,55; -35,31</t>
+          <t>-49,65; -35,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,92; 28,32</t>
+          <t>15,84; 28,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 16,78</t>
+          <t>3,63; 16,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-44,4; -34,77</t>
+          <t>-44,9; -35,35</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,42; 69,14</t>
+          <t>19,89; 66,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 25,84</t>
+          <t>-15,15; 27,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,29; -77,63</t>
+          <t>-89,01; -77,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,78; 72,8</t>
+          <t>27,61; 70,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,69; 60,32</t>
+          <t>16,76; 58,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,19; -71,76</t>
+          <t>-83,53; -72,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,55; 63,93</t>
+          <t>30,59; 63,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 36,69</t>
+          <t>7,2; 36,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,05; -77,26</t>
+          <t>-85,03; -77,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 19,71</t>
+          <t>0,73; 20,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 12,17</t>
+          <t>-8,8; 11,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-49,74; -34,45</t>
+          <t>-50,11; -34,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,01; 26,78</t>
+          <t>11,56; 27,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 14,49</t>
+          <t>-2,64; 14,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,12; -46,07</t>
+          <t>-60,53; -46,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 20,05</t>
+          <t>6,3; 19,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 10,43</t>
+          <t>-3,2; 9,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-53,66; -43,19</t>
+          <t>-53,57; -42,88</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 45,06</t>
+          <t>1,61; 50,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 29,23</t>
+          <t>-16,55; 28,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-91,91; -81,95</t>
+          <t>-91,74; -81,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,91; 44,51</t>
+          <t>16,37; 45,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 24,07</t>
+          <t>-3,78; 24,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,99; -76,07</t>
+          <t>-85,75; -76,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,32; 37,46</t>
+          <t>11,07; 37,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 19,14</t>
+          <t>-5,23; 18,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-87,97; -80,89</t>
+          <t>-87,63; -80,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 17,41</t>
+          <t>2,48; 17,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 14,63</t>
+          <t>-0,9; 13,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,09; -26,18</t>
+          <t>-40,58; -26,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 14,51</t>
+          <t>-8,98; 14,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 5,61</t>
+          <t>-21,57; 4,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,98; -36,49</t>
+          <t>-56,57; -36,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 14,95</t>
+          <t>2,7; 15,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 9,29</t>
+          <t>-3,46; 9,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-44,36; -31,2</t>
+          <t>-43,58; -31,21</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,91; 50,8</t>
+          <t>5,8; 48,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 42,1</t>
+          <t>-2,07; 39,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-94,76; -70,35</t>
+          <t>-93,57; -69,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 29,44</t>
+          <t>-14,19; 28,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 11,13</t>
+          <t>-34,93; 8,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,73; -74,14</t>
+          <t>-88,56; -73,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,91; 36,82</t>
+          <t>5,71; 39,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 23,27</t>
+          <t>-7,45; 21,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-93,26; -74,03</t>
+          <t>-94,2; -74,92</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,96; 17,85</t>
+          <t>8,17; 17,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,36; 16,95</t>
+          <t>5,78; 16,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-28,2; -20,05</t>
+          <t>-27,89; -19,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,9; 27,7</t>
+          <t>15,63; 27,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 12,59</t>
+          <t>-0,48; 11,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-45,83; 12,13</t>
+          <t>-45,91; 4,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,94; 20,45</t>
+          <t>12,87; 20,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,47; 14,84</t>
+          <t>6,54; 14,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-32,93; -0,72</t>
+          <t>-32,45; 5,78</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,69; 56,47</t>
+          <t>22,15; 54,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,29; 54,09</t>
+          <t>16,3; 51,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-76,41; -62,7</t>
+          <t>-76,04; -62,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,95; 52,09</t>
+          <t>25,68; 51,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 23,69</t>
+          <t>-0,82; 22,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,32; 23,63</t>
+          <t>-79,51; 9,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,08; 50,02</t>
+          <t>29,04; 51,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,64; 36,68</t>
+          <t>14,61; 36,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,15; -1,2</t>
+          <t>-74,74; 14,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,33; 20,44</t>
+          <t>2,56; 20,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 14,72</t>
+          <t>-0,67; 15,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-33,01; -19,28</t>
+          <t>-33,61; -19,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,67; 19,15</t>
+          <t>6,24; 19,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 11,09</t>
+          <t>-3,01; 10,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-42,38; -30,16</t>
+          <t>-43,35; -31,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,89; 17,2</t>
+          <t>7,14; 17,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 9,13</t>
+          <t>-1,19; 8,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-37,62; -28,95</t>
+          <t>-37,38; -28,59</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,48; 73,8</t>
+          <t>7,55; 74,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 50,69</t>
+          <t>-2,87; 53,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,21; -67,25</t>
+          <t>-83,97; -66,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12,73; 42,93</t>
+          <t>11,74; 44,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 25,35</t>
+          <t>-5,71; 23,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,58; -68,56</t>
+          <t>-81,72; -68,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,72; 42,09</t>
+          <t>14,9; 42,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 22,48</t>
+          <t>-2,62; 21,55</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-80,63; -70,91</t>
+          <t>-80,73; -70,75</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 12,95</t>
+          <t>-7,86; 11,97</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 21,94</t>
+          <t>-1,01; 21,53</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-19,9; -4,58</t>
+          <t>-19,08; -4,43</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,64</t>
+          <t>4,01; 13,51</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 3,84</t>
+          <t>-5,16; 4,24</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-22,06; -14,53</t>
+          <t>-21,84; -14,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,85; 12,63</t>
+          <t>3,7; 12,6</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 4,61</t>
+          <t>-3,64; 4,74</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-22,13; -15,14</t>
+          <t>-22,08; -15,18</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-43,69; 142,52</t>
+          <t>-43,64; 122,24</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 217,13</t>
+          <t>-7,16; 205,51</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-92,59; -34,85</t>
+          <t>-93,04; -27,42</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11,32; 48,24</t>
+          <t>12,63; 49,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 13,39</t>
+          <t>-15,55; 14,89</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-67,19; -50,62</t>
+          <t>-67,12; -50,85</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,47; 47,8</t>
+          <t>11,83; 47,0</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 17,16</t>
+          <t>-11,85; 17,48</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-71,12; -56,27</t>
+          <t>-71,24; -55,95</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>9,16; 15,75</t>
+          <t>8,94; 15,63</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,98; 10,45</t>
+          <t>3,81; 10,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-32,08; -26,84</t>
+          <t>-31,86; -26,84</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12,73; 18,69</t>
+          <t>12,93; 18,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,25</t>
+          <t>2,25; 8,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-34,79; -14,09</t>
+          <t>-34,89; -13,83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,81; 16,46</t>
+          <t>11,9; 16,16</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,24</t>
+          <t>3,86; 8,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-32,56; -20,36</t>
+          <t>-32,53; -20,24</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>23,81; 44,96</t>
+          <t>23,31; 44,69</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10,27; 29,88</t>
+          <t>10,13; 28,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-84,29; -76,09</t>
+          <t>-83,58; -75,65</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26,79; 42,33</t>
+          <t>27,1; 41,36</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,6; 18,46</t>
+          <t>4,94; 18,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-74,71; -30,41</t>
+          <t>-74,7; -31,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,49; 40,3</t>
+          <t>27,39; 39,85</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>9,14; 20,37</t>
+          <t>8,89; 20,25</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-77,13; -48,47</t>
+          <t>-77,13; -48,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-37,76</t>
+          <t>-37,49</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-42,49</t>
+          <t>-42,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-39,55</t>
+          <t>-39,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 27,26</t>
+          <t>9,76; 26,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 10,87</t>
+          <t>-8,21; 10,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-43,64; -31,51</t>
+          <t>-43,59; -30,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,86; 34,23</t>
+          <t>17,49; 35,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,66; 27,91</t>
+          <t>9,37; 29,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,65; -35,17</t>
+          <t>-49,71; -34,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,84; 28,28</t>
+          <t>15,75; 29,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 16,69</t>
+          <t>3,24; 17,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-44,9; -35,35</t>
+          <t>-43,85; -34,46</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-84,26%</t>
+          <t>-83,64%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-78,72%</t>
+          <t>-78,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-81,24%</t>
+          <t>-80,72%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,89; 66,94</t>
+          <t>19,61; 66,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 27,26</t>
+          <t>-16,95; 26,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,01; -77,82</t>
+          <t>-88,22; -76,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,61; 70,37</t>
+          <t>29,79; 75,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,76; 58,94</t>
+          <t>15,65; 61,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,53; -72,65</t>
+          <t>-84,05; -72,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,59; 63,67</t>
+          <t>30,43; 65,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 36,84</t>
+          <t>6,29; 37,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,03; -77,09</t>
+          <t>-84,19; -76,49</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-42,19</t>
+          <t>-41,56</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-53,06</t>
+          <t>-52,77</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-48,43</t>
+          <t>-47,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 20,75</t>
+          <t>0,47; 20,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 11,72</t>
+          <t>-8,0; 12,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-50,11; -34,75</t>
+          <t>-50,44; -34,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 27,48</t>
+          <t>10,17; 26,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 14,69</t>
+          <t>-2,61; 14,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,53; -46,13</t>
+          <t>-59,59; -45,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 19,76</t>
+          <t>6,55; 19,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 9,69</t>
+          <t>-3,08; 10,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-53,57; -42,88</t>
+          <t>-52,74; -42,77</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-87,77%</t>
+          <t>-86,46%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-81,42%</t>
+          <t>-80,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-84,72%</t>
+          <t>-83,81%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 50,54</t>
+          <t>1,0; 49,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 28,7</t>
+          <t>-15,08; 29,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-91,74; -81,76</t>
+          <t>-91,04; -80,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,37; 45,61</t>
+          <t>14,43; 43,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 24,58</t>
+          <t>-3,91; 24,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,75; -76,11</t>
+          <t>-85,31; -75,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 37,27</t>
+          <t>10,8; 37,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 18,35</t>
+          <t>-5,25; 19,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-87,63; -80,99</t>
+          <t>-86,9; -80,06</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-32,46</t>
+          <t>-28,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-46,57</t>
+          <t>-46,76</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-36,5</t>
+          <t>-33,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 17,22</t>
+          <t>2,58; 16,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 13,74</t>
+          <t>-0,84; 14,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-40,58; -26,0</t>
+          <t>-34,19; -21,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 14,03</t>
+          <t>-8,47; 14,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 4,15</t>
+          <t>-21,08; 5,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,57; -36,46</t>
+          <t>-55,86; -36,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 15,76</t>
+          <t>2,72; 15,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 9,19</t>
+          <t>-4,4; 9,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-43,58; -31,21</t>
+          <t>-38,76; -27,87</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-82,77%</t>
+          <t>-71,63%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-82,6%</t>
+          <t>-82,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-83,21%</t>
+          <t>-75,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,8; 48,35</t>
+          <t>6,58; 48,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 39,24</t>
+          <t>-1,89; 40,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-93,57; -69,71</t>
+          <t>-79,49; -61,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 28,9</t>
+          <t>-13,99; 30,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 8,27</t>
+          <t>-34,26; 10,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,56; -73,88</t>
+          <t>-88,6; -74,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,71; 39,21</t>
+          <t>5,59; 39,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 21,85</t>
+          <t>-9,3; 23,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-94,2; -74,92</t>
+          <t>-81,13; -68,62</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-24,03</t>
+          <t>-23,13</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-25,74</t>
+          <t>-43,64</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-22,45</t>
+          <t>-30,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,17; 17,61</t>
+          <t>7,42; 17,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 16,4</t>
+          <t>6,41; 16,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-27,89; -19,69</t>
+          <t>-26,86; -19,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,63; 27,04</t>
+          <t>14,77; 27,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 11,81</t>
+          <t>0,12; 12,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-45,91; 4,67</t>
+          <t>-48,82; -38,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,87; 20,67</t>
+          <t>12,79; 20,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,54; 14,9</t>
+          <t>7,08; 14,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-32,45; 5,78</t>
+          <t>-34,15; -27,54</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-70,06%</t>
+          <t>-67,44%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-45,57%</t>
+          <t>-77,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-52,61%</t>
+          <t>-72,13%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,15; 54,42</t>
+          <t>20,14; 55,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,3; 51,61</t>
+          <t>17,4; 52,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-76,04; -62,66</t>
+          <t>-72,91; -59,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,68; 51,02</t>
+          <t>24,89; 52,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 22,28</t>
+          <t>0,23; 23,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,51; 9,02</t>
+          <t>-81,16; -73,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,04; 51,26</t>
+          <t>28,62; 51,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,61; 36,41</t>
+          <t>15,57; 36,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-74,74; 14,86</t>
+          <t>-76,09; -68,27</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-25,91</t>
+          <t>-26,08</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-36,68</t>
+          <t>-33,82</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-33,14</t>
+          <t>-31,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 20,62</t>
+          <t>2,26; 20,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 15,42</t>
+          <t>-2,06; 14,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-33,61; -19,01</t>
+          <t>-33,14; -19,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,24; 19,32</t>
+          <t>5,86; 18,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 10,55</t>
+          <t>-2,57; 10,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-43,35; -31,17</t>
+          <t>-39,44; -28,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,14; 17,53</t>
+          <t>6,86; 17,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 8,79</t>
+          <t>-1,88; 8,54</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-37,38; -28,59</t>
+          <t>-36,41; -27,86</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-76,63%</t>
+          <t>-77,13%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-74,99%</t>
+          <t>-69,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-75,64%</t>
+          <t>-72,37%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,55; 74,6</t>
+          <t>5,51; 70,77</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 53,01</t>
+          <t>-5,01; 53,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,97; -66,4</t>
+          <t>-83,8; -67,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,74; 44,24</t>
+          <t>11,39; 41,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 23,27</t>
+          <t>-4,94; 23,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,72; -68,75</t>
+          <t>-73,93; -62,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,9; 42,84</t>
+          <t>14,16; 42,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 21,55</t>
+          <t>-4,02; 20,95</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-80,73; -70,75</t>
+          <t>-76,53; -67,86</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-11,26</t>
+          <t>-10,36</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-18,19</t>
+          <t>-17,57</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-18,58</t>
+          <t>-17,72</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 11,97</t>
+          <t>-7,76; 12,44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 21,53</t>
+          <t>-1,3; 21,61</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -4,43</t>
+          <t>-19,22; -3,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,01; 13,51</t>
+          <t>4,24; 13,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 4,24</t>
+          <t>-5,14; 3,98</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-21,84; -14,49</t>
+          <t>-21,48; -13,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,7; 12,6</t>
+          <t>3,56; 12,08</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 4,74</t>
+          <t>-3,81; 4,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-22,08; -15,18</t>
+          <t>-21,29; -14,12</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-76,11%</t>
+          <t>-70,04%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-59,47%</t>
+          <t>-57,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-64,42%</t>
+          <t>-61,43%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-43,64; 122,24</t>
+          <t>-41,2; 131,89</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 205,51</t>
+          <t>-7,6; 226,8</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-93,04; -27,42</t>
+          <t>-90,83; -23,02</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12,63; 49,02</t>
+          <t>13,04; 49,86</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 14,89</t>
+          <t>-15,79; 13,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-67,12; -50,85</t>
+          <t>-65,2; -47,43</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,83; 47,0</t>
+          <t>11,63; 45,88</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 17,48</t>
+          <t>-12,71; 17,67</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-71,24; -55,95</t>
+          <t>-68,99; -53,15</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-29,31</t>
+          <t>-28,14</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-28,87</t>
+          <t>-32,95</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-29,37</t>
+          <t>-30,91</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>8,94; 15,63</t>
+          <t>9,25; 15,23</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,1</t>
+          <t>4,05; 10,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-31,86; -26,84</t>
+          <t>-30,56; -25,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12,93; 18,49</t>
+          <t>12,95; 18,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,25; 8,32</t>
+          <t>2,27; 8,12</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-34,89; -13,83</t>
+          <t>-35,08; -30,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,9; 16,16</t>
+          <t>12,07; 16,35</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,26</t>
+          <t>4,01; 8,36</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-32,53; -20,24</t>
+          <t>-32,57; -29,12</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-79,21%</t>
+          <t>-76,04%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-62,79%</t>
+          <t>-71,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-70,09%</t>
+          <t>-73,75%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>23,31; 44,69</t>
+          <t>23,95; 43,07</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10,13; 28,94</t>
+          <t>10,42; 28,59</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-83,58; -75,65</t>
+          <t>-78,95; -72,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27,1; 41,36</t>
+          <t>27,25; 41,58</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,94; 18,88</t>
+          <t>4,81; 18,47</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-74,7; -31,15</t>
+          <t>-74,44; -69,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,39; 39,85</t>
+          <t>27,9; 40,21</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8,89; 20,25</t>
+          <t>9,39; 20,47</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-77,13; -48,05</t>
+          <t>-75,8; -71,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
